--- a/2026/SAENZ PEÑA/Mayo/SAENZ_EXPENSAS-Mayo.xlsx
+++ b/2026/SAENZ PEÑA/Mayo/SAENZ_EXPENSAS-Mayo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\SAENZ PEÑA\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SAENZ PEÑA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82BBCC1-049D-4A1D-810D-84F3AABDD6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0119E445-9BE9-4D5F-B1B5-EF8213B3620C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -19,14 +19,19 @@
     <sheet name="extraordinaria" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$42</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="83">
   <si>
     <t>UF</t>
   </si>
@@ -211,9 +216,6 @@
     <t>CORRESPONDE A:</t>
   </si>
   <si>
-    <t xml:space="preserve">Pago efectivo </t>
-  </si>
-  <si>
     <t>MP:1148</t>
   </si>
   <si>
@@ -223,37 +225,61 @@
     <t>Mercantil Andina</t>
   </si>
   <si>
-    <t xml:space="preserve">Poliza 8356156-0 </t>
-  </si>
-  <si>
-    <t>Honorarios</t>
-  </si>
-  <si>
     <t>Prevision</t>
   </si>
   <si>
     <t>PRESUPUESTO APROBADO - MANO DE OBRA GAS Y CLOACAS</t>
   </si>
   <si>
-    <t>Federacion Patronal - Sra. Nancy - Poliza 9200959</t>
-  </si>
-  <si>
     <t>Subidos en En3r0</t>
   </si>
   <si>
     <t xml:space="preserve">  </t>
   </si>
   <si>
-    <t>Desagote de Pozo - Camiones Villar</t>
-  </si>
-  <si>
     <t>Liquidacion mes de MAYO</t>
   </si>
   <si>
     <t xml:space="preserve">Período MAYO </t>
   </si>
   <si>
-    <t>Destapacion en Saenz peña - Forlini nora</t>
+    <t>Poliza 8356156-0 - Abril</t>
+  </si>
+  <si>
+    <t>Poliza 8356156-0 - Mayo</t>
+  </si>
+  <si>
+    <t>Honorarios Abril</t>
+  </si>
+  <si>
+    <t>Honorarios Mayo</t>
+  </si>
+  <si>
+    <t>Federacion Patronal - Sra. Nancy - Poliza 9200959 - Poliza que se dara de baja ya que esta unido a la CUIT de la administracion - Cubierta hasta el 31/05 - Periodo Abril</t>
+  </si>
+  <si>
+    <t>Federacion Patronal - Sra. Nancy - Poliza 9200959 - Poliza que se dara de baja ya que esta unido a la CUIT de la administracion - Cubierta hasta el 31/05 - Periodo Mayo</t>
+  </si>
+  <si>
+    <t>Periodo Abril</t>
+  </si>
+  <si>
+    <t>Periodo Mayo</t>
+  </si>
+  <si>
+    <t>Destapacion - 22/04 Destapacion de cañeria cloacal desde camara hacia onodor en dpto B y desde camara hacia pozo. Se extrajo papel higenico - Dia 25/04: Destapacio de inodoro en dpto B - Se extrajo un trap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Período Abril </t>
+  </si>
+  <si>
+    <t>Desagote de Pozo - Camiones Villar 24/04</t>
+  </si>
+  <si>
+    <t>Materiales de construccion - Cascote picado en bolson</t>
+  </si>
+  <si>
+    <t>Pago finalizacion de obra cloacal (Restaban abonar $500.00 al cierre de la obra) - Ver resumen de octubre</t>
   </si>
 </sst>
 </file>
@@ -434,7 +460,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="51">
+  <borders count="52">
     <border>
       <left/>
       <right/>
@@ -1066,13 +1092,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1287,6 +1324,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1353,8 +1395,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1433,9 +1495,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1473,9 +1535,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1508,9 +1570,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1543,9 +1622,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1722,53 +1818,53 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H70"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="97" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D6" s="28"/>
       <c r="E6" s="28" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F6" s="28"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>43</v>
       </c>
@@ -1776,11 +1872,11 @@
       <c r="C7" s="59"/>
       <c r="D7" s="59"/>
       <c r="E7" s="24" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F7" s="98"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1788,24 +1884,24 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="101" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="97"/>
       <c r="C11" s="12"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="128" t="s">
+      <c r="E11" s="131" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="128"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F11" s="131"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="99"/>
       <c r="B12" s="99"/>
       <c r="C12" s="105"/>
@@ -1817,14 +1913,14 @@
         <v>1810783.8092361402</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="97" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="97" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" s="150">
+        <v>70</v>
+      </c>
+      <c r="C13" s="129">
         <v>40499</v>
       </c>
       <c r="D13" s="36"/>
@@ -1833,314 +1929,403 @@
       </c>
       <c r="F13" s="50">
         <f>'prorrateo '!F11</f>
-        <v>377450.204562</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="99" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="99" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="150">
-        <v>64087.45</v>
-      </c>
-      <c r="D14" s="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="97" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="97" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="129">
+        <v>40499</v>
+      </c>
+      <c r="D14" s="36"/>
       <c r="E14" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="50">
-        <f>-(C36)</f>
-        <v>-578954.44999999995</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="97" t="s">
+      <c r="F14" s="160">
+        <f>-(C42)</f>
+        <v>-917075.27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="99" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="99" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="129">
+        <v>38128.82</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="158" t="s">
+        <v>82</v>
+      </c>
+      <c r="F15" s="159">
+        <v>-500000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="99" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="99" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="129">
+        <v>64087.45</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="158"/>
+      <c r="F16" s="159"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="97" t="s">
+      <c r="B17" s="97" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="130">
+        <v>35000</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="50"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="97" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="97" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="130">
+        <v>35000</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="50"/>
+    </row>
+    <row r="19" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="153" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="154"/>
+      <c r="C19" s="130">
+        <v>10568</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="50"/>
+    </row>
+    <row r="20" spans="1:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="153" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="154"/>
+      <c r="C20" s="130">
+        <v>10568</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="50"/>
+      <c r="H20" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="71">
-        <v>35000</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="50"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="99" t="s">
-        <v>69</v>
-      </c>
-      <c r="B16" s="97"/>
-      <c r="C16" s="151">
-        <v>10568</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="50"/>
-      <c r="H16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="102"/>
-      <c r="B17" s="103"/>
-      <c r="C17" s="125">
-        <f>SUM(C12:C16)</f>
-        <v>150154.45000000001</v>
-      </c>
-      <c r="E17" s="51" t="s">
+    </row>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="102"/>
+      <c r="B21" s="103"/>
+      <c r="C21" s="125">
+        <f>SUM(C12:C20)</f>
+        <v>274350.27</v>
+      </c>
+      <c r="E21" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="118">
-        <f>SUM(F12:F15)</f>
-        <v>1609279.56379814</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="101" t="s">
+      <c r="F21" s="118">
+        <f>SUM(F12:F17)</f>
+        <v>393708.5392361402</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="97"/>
-      <c r="C18" s="126"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="20"/>
-    </row>
-    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="97" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="104" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="71">
-        <v>88800</v>
-      </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="20"/>
-    </row>
-    <row r="20" spans="1:7" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="129" t="s">
-        <v>75</v>
-      </c>
-      <c r="B20" s="130"/>
-      <c r="C20" s="151">
-        <v>120000</v>
-      </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="20"/>
-    </row>
-    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="97" t="s">
-        <v>72</v>
-      </c>
-      <c r="B21" s="104"/>
-      <c r="C21" s="105">
-        <v>220000</v>
-      </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="20"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="97" t="s">
-        <v>67</v>
-      </c>
-      <c r="B22" s="104"/>
-      <c r="C22" s="105"/>
+      <c r="B22" s="97"/>
+      <c r="C22" s="126"/>
       <c r="D22" s="5"/>
       <c r="E22" s="19"/>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="102"/>
-      <c r="B23" s="103"/>
-      <c r="C23" s="119">
-        <f>SUM(C18:C22)</f>
-        <v>428800</v>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="97" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="104" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="130">
+        <v>88800</v>
       </c>
       <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="6"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="41"/>
-      <c r="C24" s="120">
-        <f>+C23+C17</f>
-        <v>578954.44999999995</v>
+      <c r="E23" s="19"/>
+      <c r="F23" s="20"/>
+    </row>
+    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="97" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="104" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="130">
+        <v>88800</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="60" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="73"/>
-      <c r="C25" s="74"/>
+    <row r="25" spans="1:8" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="155" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="156"/>
+      <c r="C25" s="130">
+        <v>210000</v>
+      </c>
+      <c r="D25" s="5"/>
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="22" t="s">
+    <row r="26" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="132" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="133"/>
+      <c r="C26" s="130">
+        <v>35125</v>
+      </c>
+      <c r="D26" s="5"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="20"/>
+    </row>
+    <row r="27" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="128" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" s="157"/>
+      <c r="C27" s="130">
+        <v>220000</v>
+      </c>
+      <c r="D27" s="5"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="20"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="97" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="104"/>
+      <c r="C28" s="105"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="20"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="102"/>
+      <c r="B29" s="103"/>
+      <c r="C29" s="119">
+        <f>SUM(C22:C28)</f>
+        <v>642725</v>
+      </c>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="6"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="41"/>
+      <c r="C30" s="120">
+        <f>+C29+C21</f>
+        <v>917075.27</v>
+      </c>
+      <c r="D30" s="5"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="20"/>
+    </row>
+    <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="60" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="37"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="46"/>
-      <c r="F27" s="6"/>
-    </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="44"/>
-      <c r="B28" s="43"/>
-      <c r="C28" s="45">
-        <v>0</v>
-      </c>
-      <c r="F28" s="6"/>
-    </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="52"/>
-      <c r="B29" s="53"/>
-      <c r="C29" s="45">
-        <v>0</v>
-      </c>
-      <c r="F29" s="6"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="69"/>
-      <c r="B30" s="70"/>
-      <c r="C30" s="72"/>
-      <c r="F30" s="6"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="69"/>
-      <c r="B31" s="76"/>
-      <c r="C31" s="77"/>
-      <c r="F31" s="6"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="69"/>
-      <c r="B32" s="75"/>
-      <c r="C32" s="72">
-        <v>0</v>
-      </c>
-      <c r="F32" s="6"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="54" t="s">
+      <c r="B31" s="73"/>
+      <c r="C31" s="74"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="20"/>
+    </row>
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="37"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="46"/>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="44"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="45">
+        <v>0</v>
+      </c>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="52"/>
+      <c r="B35" s="53"/>
+      <c r="C35" s="45">
+        <v>0</v>
+      </c>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="69"/>
+      <c r="B36" s="70"/>
+      <c r="C36" s="72"/>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="69"/>
+      <c r="B37" s="76"/>
+      <c r="C37" s="77"/>
+      <c r="F37" s="6"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="69"/>
+      <c r="B38" s="75"/>
+      <c r="C38" s="72">
+        <v>0</v>
+      </c>
+      <c r="F38" s="6"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="B33" s="55"/>
-      <c r="C33" s="56">
-        <f>SUM(C28:C32)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="B39" s="55"/>
+      <c r="C39" s="56">
+        <f>SUM(C34:C38)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="122">
-        <f>C24-C22</f>
-        <v>578954.44999999995</v>
-      </c>
-      <c r="F34" s="6"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
+      <c r="C40" s="122">
+        <f>C30-C28</f>
+        <v>917075.27</v>
+      </c>
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C35" s="123">
-        <f>+C24</f>
-        <v>578954.44999999995</v>
-      </c>
-      <c r="E35" s="100"/>
-      <c r="F35" s="6"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="54" t="s">
+      <c r="C41" s="123">
+        <f>+C30</f>
+        <v>917075.27</v>
+      </c>
+      <c r="E41" s="100"/>
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="55"/>
-      <c r="C36" s="124">
-        <f>C34</f>
-        <v>578954.44999999995</v>
-      </c>
-      <c r="E36" s="16"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D41" s="6"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D42" s="16"/>
+      <c r="B42" s="55"/>
+      <c r="C42" s="124">
+        <f>C40</f>
+        <v>917075.27</v>
+      </c>
       <c r="E42" s="16"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D44" s="16"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D45" s="16"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="19"/>
-      <c r="B57" s="18"/>
-      <c r="C57" s="20"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="18"/>
-      <c r="B58" s="18"/>
-      <c r="C58" s="18"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="18"/>
-      <c r="B59" s="18"/>
-      <c r="C59" s="18"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="18"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="18"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="18"/>
-      <c r="B61" s="18"/>
-      <c r="C61" s="18"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="18"/>
-      <c r="B62" s="18"/>
-      <c r="C62" s="18"/>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="18"/>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D47" s="6"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D50" s="16"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D51" s="16"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="19"/>
       <c r="B63" s="18"/>
-      <c r="C63" s="18"/>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C63" s="20"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
     </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="18"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="18"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="18"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="18"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="18"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="18"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="18"/>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="7">
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:F16"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2158,24 +2343,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="95" t="s">
         <v>60</v>
       </c>
@@ -2197,7 +2382,7 @@
       </c>
       <c r="L1" s="27"/>
     </row>
-    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="63" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de MAYO</v>
@@ -2216,7 +2401,7 @@
       <c r="K2" s="67"/>
       <c r="L2" s="68"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2254,7 +2439,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2284,7 +2469,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2300,7 +2485,9 @@
       <c r="E5" s="34">
         <v>652249.57843237906</v>
       </c>
-      <c r="F5" s="127"/>
+      <c r="F5" s="127">
+        <v>0</v>
+      </c>
       <c r="G5" s="58">
         <f>E5-F5</f>
         <v>652249.57843237906</v>
@@ -2325,7 +2512,7 @@
         <v>763291.22235669894</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2342,16 +2529,15 @@
         <v>58373.316057000011</v>
       </c>
       <c r="F6" s="127">
-        <f>'detalle y gastos'!C20</f>
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="G6" s="58">
         <f t="shared" ref="G6:G8" si="0">E6-F6</f>
-        <v>-61626.683942999989</v>
+        <v>58373.316057000011</v>
       </c>
       <c r="H6" s="61">
         <f t="shared" ref="H6:H10" si="1">IF(G6&gt;0,G6*8.4%,0)</f>
-        <v>0</v>
+        <v>4903.3585487880009</v>
       </c>
       <c r="I6" s="15">
         <v>0</v>
@@ -2366,10 +2552,10 @@
       </c>
       <c r="L6" s="32">
         <f>J6+K6+H6+G6</f>
-        <v>-3253.3678859999782</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>121649.99066278801</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2386,16 +2572,15 @@
         <v>58856.970046000009</v>
       </c>
       <c r="F7" s="127">
-        <f>E7</f>
-        <v>58856.970046000009</v>
+        <v>0</v>
       </c>
       <c r="G7" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>58856.970046000009</v>
       </c>
       <c r="H7" s="61">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4943.9854838640013</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
@@ -2410,10 +2595,10 @@
       </c>
       <c r="L7" s="32">
         <f t="shared" ref="L7:L9" si="2">J7+K7+H7+G7</f>
-        <v>58856.970046000009</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <v>122657.92557586402</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2430,16 +2615,15 @@
         <v>73664.222940000007</v>
       </c>
       <c r="F8" s="127">
-        <f>E8</f>
-        <v>73664.222940000007</v>
+        <v>0</v>
       </c>
       <c r="G8" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>73664.222940000007</v>
       </c>
       <c r="H8" s="61">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6187.7947269600008</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
@@ -2454,10 +2638,10 @@
       </c>
       <c r="L8" s="32">
         <f t="shared" si="2"/>
-        <v>73664.222940000007</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <v>153516.24060696003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2474,16 +2658,15 @@
         <v>59229.011576000004</v>
       </c>
       <c r="F9" s="127">
-        <f>E9</f>
-        <v>59229.011576000004</v>
+        <v>0</v>
       </c>
       <c r="G9" s="58">
         <f>E9-F9</f>
-        <v>0</v>
+        <v>59229.011576000004</v>
       </c>
       <c r="H9" s="61">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4975.2369723840011</v>
       </c>
       <c r="I9" s="15">
         <v>0</v>
@@ -2498,10 +2681,10 @@
       </c>
       <c r="L9" s="32">
         <f t="shared" si="2"/>
-        <v>59229.011576000004</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+        <v>123433.26012438402</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>6</v>
       </c>
@@ -2518,15 +2701,15 @@
         <v>65665.330044999995</v>
       </c>
       <c r="F10" s="127">
-        <v>65700</v>
+        <v>0</v>
       </c>
       <c r="G10" s="58">
         <f>E10-F10</f>
-        <v>-34.669955000004848</v>
+        <v>65665.330044999995</v>
       </c>
       <c r="H10" s="61">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5515.8877237799998</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
@@ -2541,10 +2724,10 @@
       </c>
       <c r="L10" s="32">
         <f>J10+K10+H10+G10</f>
-        <v>65630.66008999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>136846.54781377999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>10</v>
       </c>
@@ -2560,15 +2743,15 @@
       </c>
       <c r="F11" s="35">
         <f>SUM(F5:F10)</f>
-        <v>377450.204562</v>
+        <v>0</v>
       </c>
       <c r="G11" s="42">
         <f>SUM(G5:G10)</f>
-        <v>590588.22453437897</v>
+        <v>968038.42909637897</v>
       </c>
       <c r="H11" s="42">
         <f t="shared" ref="H11:K11" si="4">SUM(H5:H10)</f>
-        <v>54788.964588319846</v>
+        <v>81315.228044095842</v>
       </c>
       <c r="I11" s="11">
         <f t="shared" si="4"/>
@@ -2584,27 +2767,27 @@
       </c>
       <c r="L11" s="42">
         <f>SUM(L5:L10)</f>
-        <v>1017418.719122699</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="131"/>
-      <c r="B12" s="131"/>
-      <c r="C12" s="131"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="131"/>
-      <c r="F12" s="131"/>
-      <c r="G12" s="131"/>
-      <c r="H12" s="131"/>
-      <c r="I12" s="131"/>
-      <c r="J12" s="131"/>
-      <c r="K12" s="131"/>
-      <c r="L12" s="131"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1421395.1871404748</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="134"/>
+      <c r="B12" s="134"/>
+      <c r="C12" s="134"/>
+      <c r="D12" s="134"/>
+      <c r="E12" s="134"/>
+      <c r="F12" s="134"/>
+      <c r="G12" s="134"/>
+      <c r="H12" s="134"/>
+      <c r="I12" s="134"/>
+      <c r="J12" s="134"/>
+      <c r="K12" s="134"/>
+      <c r="L12" s="134"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L13" s="6"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
     </row>
@@ -2624,36 +2807,36 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="106" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B1" s="107"/>
       <c r="C1" s="107"/>
       <c r="D1" s="108"/>
       <c r="E1" s="109"/>
       <c r="F1" s="108"/>
-      <c r="G1" s="132">
+      <c r="G1" s="135">
         <v>4500000</v>
       </c>
-      <c r="H1" s="132"/>
+      <c r="H1" s="135"/>
       <c r="I1" s="110"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
@@ -2682,7 +2865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -2703,7 +2886,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="12">
         <v>1</v>
       </c>
@@ -2735,7 +2918,7 @@
         <v>680400</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>2</v>
       </c>
@@ -2767,7 +2950,7 @@
         <v>706050</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>3</v>
       </c>
@@ -2799,7 +2982,7 @@
         <v>711900</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>4</v>
       </c>
@@ -2831,7 +3014,7 @@
         <v>891000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>5</v>
       </c>
@@ -2863,7 +3046,7 @@
         <v>716400</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>6</v>
       </c>
@@ -2895,7 +3078,7 @@
         <v>794250</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="113" t="s">
         <v>10</v>
       </c>
@@ -2926,21 +3109,21 @@
         <v>4500000</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="131"/>
-      <c r="B11" s="131"/>
-      <c r="C11" s="131"/>
-      <c r="D11" s="131"/>
-      <c r="E11" s="131"/>
-      <c r="F11" s="131"/>
-      <c r="G11" s="131"/>
-      <c r="H11" s="131"/>
-      <c r="I11" s="131"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="134"/>
+      <c r="B11" s="134"/>
+      <c r="C11" s="134"/>
+      <c r="D11" s="134"/>
+      <c r="E11" s="134"/>
+      <c r="F11" s="134"/>
+      <c r="G11" s="134"/>
+      <c r="H11" s="134"/>
+      <c r="I11" s="134"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I12" s="6"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
     </row>
@@ -2958,68 +3141,68 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="138" t="s">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="141" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="140"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="143"/>
       <c r="F1" s="78"/>
       <c r="G1" s="78"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="141" t="s">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="144" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="142"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="144">
+      <c r="B2" s="145"/>
+      <c r="C2" s="146"/>
+      <c r="D2" s="147">
         <v>565</v>
       </c>
-      <c r="E2" s="145"/>
+      <c r="E2" s="148"/>
       <c r="F2" s="79"/>
       <c r="G2" s="79"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="146" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="146" t="s">
+    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="149" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="149" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="146" t="s">
+      <c r="C3" s="149" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="148" t="s">
+      <c r="D3" s="151" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="133" t="s">
+      <c r="E3" s="136" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="133" t="s">
+      <c r="F3" s="136" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="133" t="s">
+      <c r="G3" s="136" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="147"/>
-      <c r="B4" s="147"/>
-      <c r="C4" s="147"/>
-      <c r="D4" s="149"/>
-      <c r="E4" s="134"/>
-      <c r="F4" s="134"/>
-      <c r="G4" s="134"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="150"/>
+      <c r="B4" s="150"/>
+      <c r="C4" s="150"/>
+      <c r="D4" s="152"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="80">
         <v>1</v>
       </c>
@@ -3042,7 +3225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="80">
         <v>2</v>
       </c>
@@ -3065,7 +3248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="80">
         <v>3</v>
       </c>
@@ -3088,7 +3271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="80">
         <v>4</v>
       </c>
@@ -3111,7 +3294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="80">
         <v>5</v>
       </c>
@@ -3134,7 +3317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="85">
         <v>6</v>
       </c>
@@ -3157,7 +3340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="90" t="s">
         <v>10</v>
       </c>
@@ -3176,12 +3359,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="135"/>
-      <c r="B12" s="136"/>
-      <c r="C12" s="136"/>
-      <c r="D12" s="136"/>
-      <c r="E12" s="137"/>
+    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="138"/>
+      <c r="B12" s="139"/>
+      <c r="C12" s="139"/>
+      <c r="D12" s="139"/>
+      <c r="E12" s="140"/>
       <c r="F12" s="78"/>
       <c r="G12" s="78"/>
     </row>
